--- a/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida</t>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 54,87</t>
+          <t>40,05; 54,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 47,0</t>
+          <t>28,41; 47,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,08; 48,6</t>
+          <t>35,84; 48,49</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 45,65</t>
+          <t>32,87; 46,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,64; 46,85</t>
+          <t>34,73; 47,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,87; 44,72</t>
+          <t>36,11; 44,5</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,78; 55,03</t>
+          <t>40,16; 55,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,13; 53,7</t>
+          <t>38,93; 54,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,25; 51,78</t>
+          <t>41,23; 51,62</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,67; 47,99</t>
+          <t>34,76; 48,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,43; 52,73</t>
+          <t>38,39; 52,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,75; 48,11</t>
+          <t>38,53; 48,18</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,09; 46,81</t>
+          <t>39,98; 46,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,55; 46,41</t>
+          <t>39,13; 46,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,47; 45,43</t>
+          <t>40,09; 45,5</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>53756</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52209</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105965</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>45278; 62134</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38734; 65418</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89388; 120951</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>72719</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>172960</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>60568; 85233</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85582; 116120</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155530; 191660</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>75564</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83871</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159434</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>64280; 88643</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70529; 99502</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140688; 176133</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>66283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>145503</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>55750; 77578</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67241; 91403</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>129270; 161655</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>268322</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>315541</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583863</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>246961; 290031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>289224; 343369</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>543972; 617390</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,05; 54,96</t>
+          <t>40,19; 55,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,41; 47,98</t>
+          <t>27,51; 47,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,84; 48,49</t>
+          <t>35,91; 48,87</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,87; 46,25</t>
+          <t>32,72; 45,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,73; 47,13</t>
+          <t>35,36; 47,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,11; 44,5</t>
+          <t>35,67; 44,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,16; 55,38</t>
+          <t>39,61; 54,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,93; 54,93</t>
+          <t>38,9; 53,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,23; 51,62</t>
+          <t>41,25; 51,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,76; 48,37</t>
+          <t>34,48; 47,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,39; 52,19</t>
+          <t>38,77; 52,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 48,18</t>
+          <t>39,07; 49,06</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,98; 46,95</t>
+          <t>40,0; 46,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,13; 46,46</t>
+          <t>39,33; 46,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,09; 45,5</t>
+          <t>40,65; 45,64</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45278; 62134</t>
+          <t>45434; 62551</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38734; 65418</t>
+          <t>37506; 65013</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89388; 120951</t>
+          <t>89570; 121898</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60568; 85233</t>
+          <t>60304; 84444</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85582; 116120</t>
+          <t>87133; 116236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155530; 191660</t>
+          <t>153628; 193593</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64280; 88643</t>
+          <t>63389; 87848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70529; 99502</t>
+          <t>70461; 97474</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140688; 176133</t>
+          <t>140757; 176698</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55750; 77578</t>
+          <t>55304; 76207</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67241; 91403</t>
+          <t>67899; 92536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129270; 161655</t>
+          <t>131074; 164606</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>246961; 290031</t>
+          <t>247107; 288013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>289224; 343369</t>
+          <t>290695; 342775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>543972; 617390</t>
+          <t>551504; 619270</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 55,33</t>
+          <t>30,98; 49,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 47,68</t>
+          <t>40,19; 54,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 48,87</t>
+          <t>38,03; 49,82</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,72; 45,82</t>
+          <t>34,84; 47,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,36; 47,17</t>
+          <t>35,15; 48,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,67; 44,95</t>
+          <t>36,88; 45,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,61; 54,89</t>
+          <t>40,32; 55,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,9; 53,81</t>
+          <t>41,49; 55,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,25; 51,79</t>
+          <t>42,98; 53,04</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,48; 47,52</t>
+          <t>39,57; 52,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,77; 52,84</t>
+          <t>33,99; 46,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,07; 49,06</t>
+          <t>38,43; 47,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,62</t>
+          <t>39,61; 47,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,38</t>
+          <t>40,6; 47,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,65; 45,64</t>
+          <t>41,44; 46,23</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52209</t>
+          <t>55652</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105965</t>
+          <t>105633</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45434; 62551</t>
+          <t>37953; 60816</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37506; 65013</t>
+          <t>46925; 64127</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89570; 121898</t>
+          <t>90989; 119188</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>72719</t>
+          <t>94378</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172960</t>
+          <t>168004</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60304; 84444</t>
+          <t>80160; 108688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87133; 116236</t>
+          <t>62767; 85778</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153628; 193593</t>
+          <t>150724; 186659</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75564</t>
+          <t>79325</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>73104</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159434</t>
+          <t>152429</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63389; 87848</t>
+          <t>66382; 92192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70461; 97474</t>
+          <t>62627; 84108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140757; 176698</t>
+          <t>135640; 167381</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>66283</t>
+          <t>74763</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79220</t>
+          <t>63925</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>138688</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55304; 76207</t>
+          <t>64935; 86752</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67899; 92536</t>
+          <t>54272; 74786</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131074; 164606</t>
+          <t>124416; 154024</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>401</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>268322</t>
+          <t>298448</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>247107; 288013</t>
+          <t>269880; 323279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>290695; 342775</t>
+          <t>245993; 285743</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>551504; 619270</t>
+          <t>533428; 595068</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47,67%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>30,98; 49,65</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40,19; 54,93</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38,03; 49,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>41,02%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>34,84; 47,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>35,15; 48,03</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36,88; 45,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>48,18%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>48,43%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>40,32; 55,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>41,49; 55,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42,98; 53,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40,04%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>39,57; 52,86</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33,99; 46,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38,43; 47,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>43,8%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>39,61; 47,45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>40,6; 47,16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41,44; 46,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4080481467090222</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4766974211333496</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4415485473873151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55652</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>105633</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3098463509032549</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4019428917288151</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.3803335321331676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>37953; 60816</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46925; 64127</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>90989; 119188</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.496503335076</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5492930619312517</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.49820488234799</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4101893532979066</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4122825702228251</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4111040582588831</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>94378</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73625</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>168004</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.3483928455105347</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3514789159531935</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.3688197979874039</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>80160; 108688</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>62767; 85778</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>150724; 186659</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4723848713150239</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4803309725193209</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4567529320428582</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4817617319369788</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4843441516155094</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4829967980127217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>79325</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>73104</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152429</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.403155314853041</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4149316731072836</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.429795656639239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>66382; 92192</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>62627; 84108</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>135640; 167381</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5599047566056039</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5572477373881957</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5303719545446386</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4555673886535415</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4003947418705917</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4283606796494646</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>74763</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>63925</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138688</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3956816078699139</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3399360482939241</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3842796468248377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>64935; 86752</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54272; 74786</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>124416; 154024</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5286218404981302</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4684223336435881</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4757292218648179</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4380309296072232</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4395120082384555</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.438728077316637</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>298448</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>266306</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>564755</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3961016589335272</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.405987134212531</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4143918140926462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>269880; 323279</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>245993; 285743</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>533428; 595068</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4744745965083328</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.471590512930327</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4622767947937819</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>49981</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>55652</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>105633</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>37953</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>46925</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>90989</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>60816</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>64127</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>119188</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>94378</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>73625</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>168004</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>80160</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>62767</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>150724</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>108688</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>85778</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>186659</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>79325</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>73104</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>152429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>66382</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>62627</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>135640</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>92192</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>84108</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>167381</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>74763</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>63925</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>138688</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>64935</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>54272</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>124416</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>86752</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>74786</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>154024</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>413</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>298448</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>266306</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>564755</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>269880</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>245993</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>533428</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>323279</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>285743</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>595068</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>